--- a/artfynd/A 37528-2023 artfynd.xlsx
+++ b/artfynd/A 37528-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37528-2023 artfynd.xlsx
+++ b/artfynd/A 37528-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73653160</v>
+        <v>73653151</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Abrahamsmåla Ö om, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547210.7659149136</v>
+        <v>547156</v>
       </c>
       <c r="R2" t="n">
-        <v>6317203.63026705</v>
+        <v>6317189</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +745,9 @@
           <t>2018-10-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,12 +778,7 @@
         <v>73653168</v>
       </c>
       <c r="B3" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547181.3699093843</v>
+        <v>547181</v>
       </c>
       <c r="R3" t="n">
-        <v>6317196.759260376</v>
+        <v>6317197</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +845,9 @@
           <t>2018-10-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,52 +875,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73653151</v>
+        <v>2672912</v>
       </c>
       <c r="B4" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>220204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Abrahamsmåla Ö om, Sm</t>
+          <t>Abrahamsmåla, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547155.800234691</v>
+        <v>546915</v>
       </c>
       <c r="R4" t="n">
-        <v>6317189.387194919</v>
+        <v>6317279</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,22 +940,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-10-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-10-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,9 +954,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Betesmark med nöt.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1027,6 +974,116 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>73653160</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Abrahamsmåla Ö om, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>547211</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6317204</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-10-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-10-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
